--- a/data/trans_orig/IP21-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP21-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1469</t>
+          <t>1182</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6882</t>
+          <t>6841</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7474</t>
+          <t>7437</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>3678</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11731</t>
+          <t>11517</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45686</t>
+          <t>45727</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51099</t>
+          <t>51386</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52743</t>
+          <t>52780</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58937</t>
+          <t>58910</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>101054</t>
+          <t>101268</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>109189</t>
+          <t>109107</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,74%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2381</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9235</t>
+          <t>9305</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2611</t>
+          <t>2569</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9815</t>
+          <t>9296</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6292</t>
+          <t>5763</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16038</t>
+          <t>15884</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>92327</t>
+          <t>92257</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>99181</t>
+          <t>99179</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>98942</t>
+          <t>99461</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>106146</t>
+          <t>106188</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>194281</t>
+          <t>194435</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>204027</t>
+          <t>204556</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,26%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8734</t>
+          <t>8448</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1888</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8773</t>
+          <t>8730</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4543</t>
+          <t>4670</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13773</t>
+          <t>14389</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,43%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58863</t>
+          <t>59149</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>66101</t>
+          <t>65596</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61554</t>
+          <t>61597</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>68439</t>
+          <t>68455</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>124151</t>
+          <t>123535</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>133381</t>
+          <t>133254</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,61%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>614</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5867</t>
+          <t>5844</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>1874</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8332</t>
+          <t>8598</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3306</t>
+          <t>3547</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11699</t>
+          <t>11869</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>68994</t>
+          <t>69017</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>74326</t>
+          <t>74247</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>70779</t>
+          <t>70513</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>77615</t>
+          <t>77237</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>142273</t>
+          <t>142103</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>150666</t>
+          <t>150425</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,7%</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6127</t>
+          <t>6568</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3370</t>
+          <t>4167</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6966</t>
+          <t>7332</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35725</t>
+          <t>35284</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41473</t>
+          <t>40676</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>79729</t>
+          <t>79363</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>85411</t>
+          <t>85397</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,5%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4164</t>
+          <t>4038</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>628</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>6667</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1430</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8197</t>
+          <t>8164</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>51891</t>
+          <t>52017</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>53323</t>
+          <t>53065</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>59106</t>
+          <t>59104</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>107590</t>
+          <t>107623</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>114357</t>
+          <t>114458</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6652</t>
+          <t>6672</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3592</t>
+          <t>3692</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12775</t>
+          <t>12578</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6228</t>
+          <t>5888</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>16944</t>
+          <t>16329</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>121970</t>
+          <t>121950</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>127954</t>
+          <t>127336</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>122880</t>
+          <t>123077</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>132063</t>
+          <t>131963</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>247333</t>
+          <t>247948</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>258049</t>
+          <t>258389</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>6869</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2693</t>
+          <t>2125</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10239</t>
+          <t>10194</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4597</t>
+          <t>4832</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14386</t>
+          <t>14598</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>150595</t>
+          <t>151035</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>156860</t>
+          <t>156847</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>153819</t>
+          <t>153864</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>161365</t>
+          <t>161933</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>307576</t>
+          <t>307364</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>317365</t>
+          <t>317130</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,5%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>18367</t>
+          <t>18081</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>34016</t>
+          <t>33917</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>25312</t>
+          <t>24286</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>42986</t>
+          <t>43268</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>47014</t>
+          <t>47626</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>71123</t>
+          <t>72464</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>647005</t>
+          <t>647104</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>662654</t>
+          <t>662940</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>679714</t>
+          <t>679432</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>697388</t>
+          <t>698414</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1332598</t>
+          <t>1331257</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1356707</t>
+          <t>1356095</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,61%</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2393</t>
+          <t>2674</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1585</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9329</t>
+          <t>8658</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1724</t>
+          <t>1732</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9627</t>
+          <t>9675</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55034</t>
+          <t>54753</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55480</t>
+          <t>56151</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>63210</t>
+          <t>63224</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>112609</t>
+          <t>112561</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>120512</t>
+          <t>120504</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1937</t>
+          <t>1926</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9076</t>
+          <t>9072</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3168</t>
+          <t>3203</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11105</t>
+          <t>11501</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6460</t>
+          <t>6487</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16822</t>
+          <t>16671</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>95637</t>
+          <t>95641</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>102776</t>
+          <t>102787</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>100054</t>
+          <t>99658</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>107991</t>
+          <t>107956</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>199050</t>
+          <t>199201</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>209412</t>
+          <t>209385</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,99%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>723</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6167</t>
+          <t>6779</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1434</t>
+          <t>1487</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7958</t>
+          <t>8856</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3341</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12108</t>
+          <t>11865</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,59%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62011</t>
+          <t>61399</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>67550</t>
+          <t>67455</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61935</t>
+          <t>61037</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>68459</t>
+          <t>68406</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>125963</t>
+          <t>126206</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>134730</t>
+          <t>134632</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,51%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>445</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4816</t>
+          <t>5192</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9895</t>
+          <t>9675</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2532</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12162</t>
+          <t>12224</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,64%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>72945</t>
+          <t>72569</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>77324</t>
+          <t>77316</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>72339</t>
+          <t>72559</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>80906</t>
+          <t>80784</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>147833</t>
+          <t>147771</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>157463</t>
+          <t>157389</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,37%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5076</t>
+          <t>5756</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>672</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6490</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>2071</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9063</t>
+          <t>9731</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38825</t>
+          <t>38145</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43203</t>
+          <t>43901</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>39615</t>
+          <t>39335</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>45432</t>
+          <t>45433</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>80943</t>
+          <t>80275</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>87955</t>
+          <t>87935</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,7%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>2066</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8796</t>
+          <t>8653</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4935</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2527</t>
+          <t>2192</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10705</t>
+          <t>10882</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>47189</t>
+          <t>47332</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>54469</t>
+          <t>53919</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>55310</t>
+          <t>53835</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>105525</t>
+          <t>105348</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>113703</t>
+          <t>114038</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5011</t>
+          <t>4719</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15005</t>
+          <t>14707</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2483</t>
+          <t>2546</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9550</t>
+          <t>9806</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9203</t>
+          <t>8335</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>20902</t>
+          <t>20482</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>123713</t>
+          <t>124011</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>133707</t>
+          <t>133999</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>135204</t>
+          <t>134948</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>142271</t>
+          <t>142208</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>262570</t>
+          <t>262990</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>274269</t>
+          <t>275137</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>97,06%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1403</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8316</t>
+          <t>8318</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2459</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10113</t>
+          <t>10096</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5488</t>
+          <t>5712</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15113</t>
+          <t>15676</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>156392</t>
+          <t>156390</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>163353</t>
+          <t>163305</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>160602</t>
+          <t>160619</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>168147</t>
+          <t>168256</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>320310</t>
+          <t>319747</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>329935</t>
+          <t>329711</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,3%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>20920</t>
+          <t>20332</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>38098</t>
+          <t>37653</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>25249</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>42564</t>
+          <t>43870</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>51365</t>
+          <t>49961</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>74303</t>
+          <t>76239</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>673293</t>
+          <t>673738</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>690471</t>
+          <t>691059</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>707350</t>
+          <t>706044</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>724869</t>
+          <t>724665</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1387002</t>
+          <t>1385066</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1409940</t>
+          <t>1411344</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,58%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>467</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5006</t>
+          <t>4802</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1880</t>
+          <t>1631</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9780</t>
+          <t>9313</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3033</t>
+          <t>3343</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11909</t>
+          <t>12331</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52365</t>
+          <t>52569</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56902</t>
+          <t>56904</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54682</t>
+          <t>55149</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62582</t>
+          <t>62831</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>109924</t>
+          <t>109502</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>118800</t>
+          <t>118490</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,26%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1167</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6637</t>
+          <t>6383</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>747</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7340</t>
+          <t>7291</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3011</t>
+          <t>2551</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11346</t>
+          <t>10587</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>97310</t>
+          <t>97564</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>102780</t>
+          <t>102802</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>102943</t>
+          <t>102992</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>109524</t>
+          <t>109536</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>202884</t>
+          <t>203643</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>211219</t>
+          <t>211679</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4637</t>
+          <t>4135</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>667</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5252</t>
+          <t>5604</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7577</t>
+          <t>7476</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62194</t>
+          <t>62696</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>64653</t>
+          <t>64301</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>69240</t>
+          <t>69238</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>129159</t>
+          <t>129260</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>135416</t>
+          <t>135411</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>742</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6461</t>
+          <t>6404</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>694</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6455</t>
+          <t>6030</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2090</t>
+          <t>2139</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9494</t>
+          <t>9884</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>70500</t>
+          <t>70557</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>76214</t>
+          <t>76219</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>74729</t>
+          <t>75154</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>80491</t>
+          <t>80490</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>148651</t>
+          <t>148261</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>156055</t>
+          <t>156006</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -9099,7 +9099,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4279</t>
+          <t>4925</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4688</t>
+          <t>5499</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>768</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7456</t>
+          <t>7408</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>49994</t>
+          <t>49348</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>53051</t>
+          <t>52240</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>104556</t>
+          <t>104604</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>111241</t>
+          <t>111244</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3849</t>
+          <t>3616</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12550</t>
+          <t>12247</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6294</t>
+          <t>7448</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6212</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>16402</t>
+          <t>15373</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>124824</t>
+          <t>125127</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>133525</t>
+          <t>133758</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>137778</t>
+          <t>136624</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>142897</t>
+          <t>142830</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>265044</t>
+          <t>266073</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>275234</t>
+          <t>275259</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1775</t>
+          <t>1748</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8374</t>
+          <t>8221</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1812</t>
+          <t>1528</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8425</t>
+          <t>8807</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4081</t>
+          <t>3969</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>13114</t>
+          <t>13145</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>154579</t>
+          <t>154732</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>161178</t>
+          <t>161205</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>162424</t>
+          <t>162042</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>169037</t>
+          <t>169321</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>320688</t>
+          <t>320657</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>329721</t>
+          <t>329833</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>14921</t>
+          <t>15132</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>29168</t>
+          <t>29261</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>14159</t>
+          <t>13633</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>29730</t>
+          <t>29319</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>32805</t>
+          <t>32566</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>53651</t>
+          <t>54318</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>673980</t>
+          <t>673887</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>688227</t>
+          <t>688016</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>715114</t>
+          <t>715525</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>730685</t>
+          <t>731211</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1394341</t>
+          <t>1393674</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1415187</t>
+          <t>1415426</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -10707,7 +10707,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>4007</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6048</t>
+          <t>6054</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>788</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>6765</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -10815,7 +10815,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69411</t>
+          <t>69275</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -10830,7 +10830,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -10850,7 +10850,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>73318</t>
+          <t>73312</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>144544</t>
+          <t>145883</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>151771</t>
+          <t>151860</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>433</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6749</t>
+          <t>7185</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>508</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5972</t>
+          <t>6530</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11100,7 +11100,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1679</t>
+          <t>1554</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10351</t>
+          <t>9304</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>119674</t>
+          <t>119238</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>125905</t>
+          <t>125990</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>121624</t>
+          <t>121066</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>127082</t>
+          <t>127088</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,7 +11208,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>243668</t>
+          <t>244715</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>252340</t>
+          <t>252465</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>582</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5256</t>
+          <t>5925</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11408,7 +11408,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3834</t>
+          <t>4248</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>1124</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6454</t>
+          <t>6572</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53012</t>
+          <t>52343</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57687</t>
+          <t>57686</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -11536,7 +11536,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63329</t>
+          <t>62915</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>118977</t>
+          <t>118859</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>124343</t>
+          <t>124307</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -11736,7 +11736,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2479</t>
+          <t>2833</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11751,7 +11751,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11771,7 +11771,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>2644</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11786,7 +11786,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11806,7 +11806,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3590</t>
+          <t>3513</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11821,7 +11821,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>67664</t>
+          <t>67310</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>75515</t>
+          <t>75490</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -11894,7 +11894,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>144688</t>
+          <t>144765</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -11929,7 +11929,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>356</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4620</t>
+          <t>4905</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12457,7 +12457,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3859</t>
+          <t>3840</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>967</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6169</t>
+          <t>5837</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41547</t>
+          <t>41262</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>45814</t>
+          <t>45811</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,7 +12565,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>52327</t>
+          <t>52346</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -12580,7 +12580,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>96184</t>
+          <t>96516</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>101642</t>
+          <t>101386</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>421</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5049</t>
+          <t>4839</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1750</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10832</t>
+          <t>10760</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,7 +12830,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2841</t>
+          <t>3320</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -12845,7 +12845,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>119459</t>
+          <t>119669</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>124093</t>
+          <t>124087</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>145180</t>
+          <t>145252</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>154262</t>
+          <t>154065</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12948,7 +12948,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>277679</t>
+          <t>277200</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12963,7 +12963,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4544</t>
+          <t>4291</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4600</t>
+          <t>4797</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -13251,7 +13251,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>152251</t>
+          <t>152504</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -13286,7 +13286,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>283814</t>
+          <t>283617</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -13301,7 +13301,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5003</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>15333</t>
+          <t>15592</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7477</t>
+          <t>7426</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>19516</t>
+          <t>20256</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>14264</t>
+          <t>14607</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>30799</t>
+          <t>29838</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>649591</t>
+          <t>649332</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>659921</t>
+          <t>659446</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>742456</t>
+          <t>741716</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>754495</t>
+          <t>754546</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1396097</t>
+          <t>1397058</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1412632</t>
+          <t>1412289</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
